--- a/assets/floor_4_data.xlsx
+++ b/assets/floor_4_data.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,6 +426,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -449,6 +452,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -472,6 +478,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -495,6 +504,9 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -518,17 +530,20 @@
       <c r="G5" t="str">
         <v/>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -552,45 +567,51 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>WIFI-AP-Lobby</v>
+        <v>AP16c</v>
       </c>
       <c r="B2" t="str">
         <v>AP</v>
       </c>
       <c r="C2">
-        <v>-541</v>
+        <v>-2027</v>
       </c>
       <c r="D2">
-        <v>385</v>
+        <v>-500</v>
       </c>
       <c r="E2" t="str">
-        <v>Main entrance access point</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>Active</v>
       </c>
       <c r="G2" t="str">
         <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>Salmon</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WIFI-AP-Canteen</v>
+        <v>AP17c</v>
       </c>
       <c r="B3" t="str">
         <v>AP</v>
       </c>
       <c r="C3">
-        <v>326</v>
+        <v>-1944</v>
       </c>
       <c r="D3">
-        <v>405</v>
+        <v>-121</v>
       </c>
       <c r="E3" t="str">
-        <v>Cafeteria coverage</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>Active</v>
@@ -598,86 +619,20 @@
       <c r="G3" t="str">
         <v/>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>SRV-DC-01</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Server</v>
-      </c>
-      <c r="C4">
-        <v>-625</v>
-      </c>
-      <c r="D4">
-        <v>173</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Domain Controller 1</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Active</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SRV-FS-01</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Server</v>
-      </c>
-      <c r="C5">
-        <v>-584</v>
-      </c>
-      <c r="D5">
-        <v>189</v>
-      </c>
-      <c r="E5" t="str">
-        <v>File Server 1</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Active</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>SW-IDF-01</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Switch</v>
-      </c>
-      <c r="C6">
-        <v>-624</v>
-      </c>
-      <c r="D6">
-        <v>211</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Main Distribution Frame Switch</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Active</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
+      <c r="H3" t="str">
+        <v>Salmon</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -701,6 +656,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -724,6 +682,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -747,6 +708,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -770,17 +734,20 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -804,6 +771,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -827,6 +797,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -850,6 +823,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -873,17 +849,20 @@
       <c r="G4" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -907,6 +886,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -930,6 +912,9 @@
       <c r="G2" t="str">
         <v/>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -953,6 +938,9 @@
       <c r="G3" t="str">
         <v/>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -976,6 +964,9 @@
       <c r="G4" t="str">
         <v/>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -999,17 +990,20 @@
       <c r="G5" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1033,6 +1027,9 @@
       <c r="G1" t="str">
         <v>LastAudit</v>
       </c>
+      <c r="H1" t="str">
+        <v>Color</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1056,6 +1053,9 @@
       <c r="G2" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1079,10 +1079,13 @@
       <c r="G3" t="str">
         <v>2025-12-15</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/floor_4_data.xlsx
+++ b/assets/floor_4_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EED35A-B5D2-4543-9724-E7BA1C914018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE2AE63-5E05-4A95-BBED-E40DD805502A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -70,25 +70,7 @@
     <t>AP17c</t>
   </si>
   <si>
-    <t>Vitamin A</t>
-  </si>
-  <si>
-    <t>Digital</t>
-  </si>
-  <si>
     <t>Added via Editor</t>
-  </si>
-  <si>
-    <t>Vitamin B</t>
-  </si>
-  <si>
-    <t>Analog</t>
-  </si>
-  <si>
-    <t>new</t>
-  </si>
-  <si>
-    <t>Digital Scale</t>
   </si>
   <si>
     <t>2025-12-15</t>
@@ -550,7 +532,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>-953</v>
@@ -642,7 +624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -669,69 +651,6 @@
       </c>
       <c r="H1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>-35</v>
-      </c>
-      <c r="D2">
-        <v>-259</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3">
-        <v>280</v>
-      </c>
-      <c r="D3">
-        <v>-265</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>130</v>
-      </c>
-      <c r="D4">
-        <v>-728</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -772,10 +691,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>1317</v>
@@ -784,21 +703,21 @@
         <v>-330</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>-481</v>
@@ -807,13 +726,13 @@
         <v>-555</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -834,25 +753,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>7</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
@@ -860,7 +779,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>-1284</v>
@@ -875,7 +794,7 @@
         <v>725</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>0.2</v>
@@ -898,7 +817,7 @@
         <v>725</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>0.2</v>
@@ -909,7 +828,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>-776</v>
@@ -924,7 +843,7 @@
         <v>635</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>0.2</v>
@@ -935,7 +854,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>-2698</v>
@@ -950,7 +869,7 @@
         <v>1348</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G5">
         <v>0.2</v>

--- a/assets/floor_4_data.xlsx
+++ b/assets/floor_4_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE2AE63-5E05-4A95-BBED-E40DD805502A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC99033-C007-4790-9524-15C5A981D225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="weight" sheetId="4" r:id="rId3"/>
     <sheet name="clock" sheetId="6" r:id="rId4"/>
     <sheet name="zones" sheetId="7" r:id="rId5"/>
+    <sheet name="building" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -122,6 +123,15 @@
   </si>
   <si>
     <t>Switch Room</t>
+  </si>
+  <si>
+    <t>#55ab46</t>
+  </si>
+  <si>
+    <t>RTD f4</t>
+  </si>
+  <si>
+    <t>Enfa f4</t>
   </si>
 </sst>
 </file>
@@ -881,4 +891,100 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D4A38E-063A-4645-A9C5-A2302DD3DB63}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2">
+        <v>-2703</v>
+      </c>
+      <c r="C2">
+        <v>-584</v>
+      </c>
+      <c r="D2">
+        <v>-1785</v>
+      </c>
+      <c r="E2">
+        <v>1308</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2">
+        <v>0.2</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>-1782</v>
+      </c>
+      <c r="C3">
+        <v>-194</v>
+      </c>
+      <c r="D3">
+        <v>-471</v>
+      </c>
+      <c r="E3">
+        <v>930</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>0.2</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/assets/floor_4_data.xlsx
+++ b/assets/floor_4_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC99033-C007-4790-9524-15C5A981D225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D149ED54-E688-476A-998A-EB2271B78CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,17 @@
     <sheet name="zones" sheetId="7" r:id="rId5"/>
     <sheet name="building" sheetId="8" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -937,16 +946,16 @@
         <v>32</v>
       </c>
       <c r="B2">
-        <v>-2703</v>
+        <v>-2673</v>
       </c>
       <c r="C2">
         <v>-584</v>
       </c>
       <c r="D2">
-        <v>-1785</v>
+        <v>-1755</v>
       </c>
       <c r="E2">
-        <v>1308</v>
+        <v>1344</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -963,13 +972,13 @@
         <v>33</v>
       </c>
       <c r="B3">
-        <v>-1782</v>
+        <v>-1752</v>
       </c>
       <c r="C3">
         <v>-194</v>
       </c>
       <c r="D3">
-        <v>-471</v>
+        <v>-441</v>
       </c>
       <c r="E3">
         <v>930</v>
